--- a/human_validation/judge/kor/judge_D020_S001_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D020_S001_P001__qwen3-235b_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,208 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 오늘 어떤 일로 오셨는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 네, 이 다 망가진 방으로 이사 온 뒤로 제가 계속... 뭔가를 제대로 처리를 못 하고 있어서 왔어요. 별거 아닌 일에도 사람들한테 날카롭게 굴고, 누수를 고치거나 난방 문제 처리하느라 밤을 새우고, 그러고는 겨우 몸을 끌고 출근하는데 지각을 해요. 평소에는 잘 알던 일들도 계속 망치고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 적응장애 (D020) | 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 취미 활동이나 친구들과 시간을 보내는 것처럼 평소 좋아하시던 일들이 즐겁지 않다고 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 글쎄요, 딱히 그런 걸 느낀 적은 없어요. 그러니까, 요즘 뭘 많이 하지는 않았는데, 그게 즐겁지 않아서라고는 말 못 하겠어요. 그보다는 그냥 그걸 생각할 여유나 기운이 없었던 거 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 적응장애 (D020) | 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 이곳으로 이사 오신 이후로, 거의 매일 하루 대부분 기분이 가라앉거나 우울하다고 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 매일 하루 대부분 우울했다고까지는 말 못 할 것 같아요. 이 집 때문에 속상하고 지치긴 했는데, 그런 식으로 딱히 챙겨본 적은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 적응장애 (D020) | 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 이곳으로 이사 오신 이후로, 취미나 친구들과 시간 보내는 것처럼 평소 좋아하시던 일에 흥미가 없어졌다고 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 잘 모르겠어요. 그런 걸 더 이상 좋아하지 않는다는 느낌은 딱히 못 받았어요. 그냥 이사 온 뒤로 뭘 많이 안 했을 뿐이라, 판단하기가 어려워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 적응장애 (D020) | 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 일이나 취미, 사람들과 어울리는 것처럼 평소 신경 쓰거나 즐기시던 것들에 흥미를 잃었다고 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 뚜렷하게 그렇지는 않은 것 같아요. 그러니까, 예전만큼 많이 하고 있지는 않은데, 그런 것들에 신경을 끊었다고는 말 못 하겠어요. 그보다는 요즘 거기에 집중을 못 했던 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 적응장애 (D020) | 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 이사와 관련 없는 일이 있을 때조차도, 이곳으로 이사 온 이후 기분이 지속적으로 가라앉아 있거나 삶에서 즐거움을 거의 느끼지 못했다고 말씀하시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 그렇게 지속적으로 가라앉아 있었다고는 말 못 할 것 같아요. 이사랑 이 집 때문에 스트레스를 받긴 했는데, 그래도 괜찮은 순간들은 있어요. 전반적으로 삶에서 즐거움을 전혀 못 느낀다고는 딱히 느낀 적 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 적응장애 (D020) | 범불안장애 (D011) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 이사 오신 이후 겪고 계신 어려움 대부분이 망가진 방을 처리하고 한꺼번에 모든 걸 관리하려는 것 같은, 상황에 대한 스트레스 반응이라고 말씀하시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 네, 거의 그런 것 같아요. 그 다 망가진 방으로 이사 온 뒤로 모든 게 쌓여가고 있어요. 사람들한테 날카롭게 굴고, 누수나 난방 문제 처리하느라 밤을 새우고, 그러고는 겨우 몸을 끌고 지각해서 출근하고, 평소에는 잘 처리하던 것들도 망치고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 방 문제를 직접 처리하고 있지 않을 때도 기분이나 행동에 상당한 영향을 받으신다고 느끼시나요, 아니면 그런 스트레스 요인을 다룰 때만 나타나는 것 같나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 대부분 그 방이랑 거기서 딸려온 문제들 주변에서 나타나요. 그러니까, 그 다 망가진 집으로 이사 온 뒤로 사람들한테 날카롭게 굴고, 누수나 난방 처리하느라 밤을 새우고, 그러고는 출근 지각에 평소 잘 처리하던 것들도 망치고요. 그거에 대해 생각 안 하거나 안 다루고 있을 때는 덜한데, 그 방에는 항상 뭔가가 있어서 계속 저를 따라다니는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 짜증이 나거나 집중하기 어렵거나 벅차다고 느끼는 것 같은 모든 증상들이 새 방과 관련된 문제를 다루거나 생각할 때만 나타난다고 말씀하시겠어요, 아니면 이사와 관련 없는 삶의 다른 부분에서도 나타나나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 대부분 그 방이랑 거기 들어가면서 생긴 문제들과 연결돼 있어요. 그러니까, 그 다 망가진 곳에 들어간 뒤로 사람들한테 날카롭게 굴고, 누수나 난방 처리하느라 밤을 새우고, 그러고는 겨우 몸을 끌고 지각해서 출근하고 평소 처리하던 일들을 망치고 있어요. 직장까지 좀 번지긴 하는데, 그 방 문제에서 시작되는 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>진단명: 적응장애 (D020)
 인구통계: 성별 남성 / 나이 26 / 직업상태 construction laborer / 최종학력 고등학교 중퇴
@@ -575,257 +768,29 @@
 증상 지속 기간: 1 month
 추가 요건: Symptoms must develop within 3 months of the onset of the stressor, Within 6 months of the termination of the stressor or its consequences
 주호소 증상 코드: S081
-배경 서술: 개럿은 직접 수리할 계획으로 브리지포트의 오래된 집에서 저렴한 방을 구했지만, 며칠 지나지 않아 누수 피해와 믿을 수 없는 난방, 그리고 임대료를 깎아주는 대신 비공식적으로 수리를 맡기려는 집주인을 발견하게 되었다. 처음에는 이를 또 하나의 DIY 도전 정도로 여기고 퇴근 후 자재를 사고 픽업 스포츠 모임의 친구들에게 도움을 청했지만, 다음 한 달 동안 끊임없는 문제들이 그의 직장과 사회생활에까지 번지기 시작했다. 주거 스트레스에 대한 그의 반응은 서류 마감을 놓치고, 긴급 수리로 밤을 새운 뒤 콘크리트 타설 작업에 지각하고, 현장 감독과 긴장된 언쟁을 벌일 정도로 부적응적으로 변해갔다. 감독이 그에게 팀장이 되기 위한 수습 과정이 틀어질 수 있다고 경고하자, 개럿은 지역 산업보건 의뢰를 통해 정신과 임상의를 만나는 데 동의했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 오늘 어떤 일로 오셨는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 네, 이 다 망가진 방으로 이사 온 뒤로 제가 계속... 뭔가를 제대로 처리를 못 하고 있어서 왔어요. 별거 아닌 일에도 사람들한테 날카롭게 굴고, 누수를 고치거나 난방 문제 처리하느라 밤을 새우고, 그러고는 겨우 몸을 끌고 출근하는데 지각을 해요. 평소에는 잘 알던 일들도 계속 망치고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 취미 활동이나 친구들과 시간을 보내는 것처럼 평소 좋아하시던 일들이 즐겁지 않다고 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 글쎄요, 딱히 그런 걸 느낀 적은 없어요. 그러니까, 요즘 뭘 많이 하지는 않았는데, 그게 즐겁지 않아서라고는 말 못 하겠어요. 그보다는 그냥 그걸 생각할 여유나 기운이 없었던 거 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 이곳으로 이사 오신 이후로, 거의 매일 하루 대부분 기분이 가라앉거나 우울하다고 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 매일 하루 대부분 우울했다고까지는 말 못 할 것 같아요. 이 집 때문에 속상하고 지치긴 했는데, 그런 식으로 딱히 챙겨본 적은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 이곳으로 이사 오신 이후로, 취미나 친구들과 시간 보내는 것처럼 평소 좋아하시던 일에 흥미가 없어졌다고 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 잘 모르겠어요. 그런 걸 더 이상 좋아하지 않는다는 느낌은 딱히 못 받았어요. 그냥 이사 온 뒤로 뭘 많이 안 했을 뿐이라, 판단하기가 어려워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 일이나 취미, 사람들과 어울리는 것처럼 평소 신경 쓰거나 즐기시던 것들에 흥미를 잃었다고 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 뚜렷하게 그렇지는 않은 것 같아요. 그러니까, 예전만큼 많이 하고 있지는 않은데, 그런 것들에 신경을 끊었다고는 말 못 하겠어요. 그보다는 요즘 거기에 집중을 못 했던 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 이사와 관련 없는 일이 있을 때조차도, 이곳으로 이사 온 이후 기분이 지속적으로 가라앉아 있거나 삶에서 즐거움을 거의 느끼지 못했다고 말씀하시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 그렇게 지속적으로 가라앉아 있었다고는 말 못 할 것 같아요. 이사랑 이 집 때문에 스트레스를 받긴 했는데, 그래도 괜찮은 순간들은 있어요. 전반적으로 삶에서 즐거움을 전혀 못 느낀다고는 딱히 느낀 적 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 범불안장애 (D011) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 이사 오신 이후 겪고 계신 어려움 대부분이 망가진 방을 처리하고 한꺼번에 모든 걸 관리하려는 것 같은, 상황에 대한 스트레스 반응이라고 말씀하시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 네, 거의 그런 것 같아요. 그 다 망가진 방으로 이사 온 뒤로 모든 게 쌓여가고 있어요. 사람들한테 날카롭게 굴고, 누수나 난방 문제 처리하느라 밤을 새우고, 그러고는 겨우 몸을 끌고 지각해서 출근하고, 평소에는 잘 처리하던 것들도 망치고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 방 문제를 직접 처리하고 있지 않을 때도 기분이나 행동에 상당한 영향을 받으신다고 느끼시나요, 아니면 그런 스트레스 요인을 다룰 때만 나타나는 것 같나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 대부분 그 방이랑 거기서 딸려온 문제들 주변에서 나타나요. 그러니까, 그 다 망가진 집으로 이사 온 뒤로 사람들한테 날카롭게 굴고, 누수나 난방 처리하느라 밤을 새우고, 그러고는 출근 지각에 평소 잘 처리하던 것들도 망치고요. 그거에 대해 생각 안 하거나 안 다루고 있을 때는 덜한데, 그 방에는 항상 뭔가가 있어서 계속 저를 따라다니는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 짜증이 나거나 집중하기 어렵거나 벅차다고 느끼는 것 같은 모든 증상들이 새 방과 관련된 문제를 다루거나 생각할 때만 나타난다고 말씀하시겠어요, 아니면 이사와 관련 없는 삶의 다른 부분에서도 나타나나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 대부분 그 방이랑 거기 들어가면서 생긴 문제들과 연결돼 있어요. 그러니까, 그 다 망가진 곳에 들어간 뒤로 사람들한테 날카롭게 굴고, 누수나 난방 처리하느라 밤을 새우고, 그러고는 겨우 몸을 끌고 지각해서 출근하고 평소 처리하던 일들을 망치고 있어요. 직장까지 좀 번지긴 하는데, 그 방 문제에서 시작되는 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
+배경 서술: 개럿은 직접 수리할 계획으로 브리지포트의 오래된 집에서 저렴한 방을 구했지만, 며칠 지나지 않아 누수 피해와 믿을 수 없는 난방, 그리고 임대료를 깎아주는 대신 비공식적으로 수리를 맡기려는 집주인을 발견하게 되었다. 처음에는 이를 또 하나의 DIY 도전 정도로 여기고 퇴근 후 자재를 사고 픽업 스포츠 모임의 친구들에게 도움을 청했지만, 다음 한 달 동안 끊임없는 문제들이 그의 직장과 사회생활에까지 번지기 시작했다. 주거 스트레스에 대한 그의 반응은 서류 마감을 놓치고, 긴급 수리로 밤을 새운 뒤 콘크리트 타설 작업에 지각하고, 현장 감독과 긴장된 언쟁을 벌일 정도로 부적응적으로 변해갔다. 감독이 그에게 팀장이 되기 위한 수습 과정이 틀어질 수 있다고 경고하자, 개럿은 지역 산업보건 의뢰를 통해 정신과 임상의를 만나는 데 동의했다.
+표집된 증상 목록:
+  - S081 스트레스 관련 부적응 반응: 확인 가능한 스트레스 요인에 대한 반응으로 나타나는 정서적·행동적 증상.</t>
+        </is>
+      </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 적응장애 (D020, ICD: F43.22)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: adjustment_symptoms (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
-  확인된 근거: 스트레스 관련 부적응 반응: 확인 가능한 스트레스 요인에 대한 반응으로 나타나는 정서적·행동적 증상.
-  누락: (없음)</t>
+          <t>의사의 최종 진단: 적응장애 (D020, ICD: F43.22)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: 0.5
+체크리스트 그룹: adjustment_symptoms (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
+확인된 근거:
+  - 스트레스 관련 부적응 반응: 확인 가능한 스트레스 요인에 대한 반응으로 나타나는 정서적·행동적 증상.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D020_S001_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D020_S001_P001__qwen3-235b_kor.xlsx
@@ -754,6 +754,11 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -786,11 +791,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D020_S001_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D020_S001_P001__qwen3-235b_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.2778</v>
+        <v>0.7222</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.3704</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.875</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
